--- a/data/trans_orig/P21_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P21_R-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado un servicio de urgencias en el último año en 2007</t>
+          <t>Población que ha utilizado un servicio de urgencias en el último año en 2007 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30343</t>
+          <t>29015</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52488</t>
+          <t>52134</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>43743</t>
+          <t>44437</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>70592</t>
+          <t>71159</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>79285</t>
+          <t>77731</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>114182</t>
+          <t>112387</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,05%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>220522</t>
+          <t>220876</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>242667</t>
+          <t>243995</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>190246</t>
+          <t>189679</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>217095</t>
+          <t>216401</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>419666</t>
+          <t>421461</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>454563</t>
+          <t>456117</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>85,44%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>60064</t>
+          <t>61937</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>95428</t>
+          <t>94979</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>107387</t>
+          <t>110331</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>147912</t>
+          <t>147318</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>178765</t>
+          <t>178556</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>229501</t>
+          <t>228189</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,89%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>397647</t>
+          <t>398096</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>433011</t>
+          <t>431138</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>356037</t>
+          <t>356631</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>396562</t>
+          <t>393618</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>767523</t>
+          <t>768835</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>818259</t>
+          <t>818468</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>82,09%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>54828</t>
+          <t>54943</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>84954</t>
+          <t>84804</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>70724</t>
+          <t>70582</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>102754</t>
+          <t>102957</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>132553</t>
+          <t>132411</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>176313</t>
+          <t>176963</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>27,05%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>233892</t>
+          <t>234042</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>264018</t>
+          <t>263903</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>73,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>232658</t>
+          <t>232455</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>264688</t>
+          <t>264830</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>477945</t>
+          <t>477295</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>521705</t>
+          <t>521847</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>79,76%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>60831</t>
+          <t>61117</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>90782</t>
+          <t>91043</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>87258</t>
+          <t>87877</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>121544</t>
+          <t>121760</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>157301</t>
+          <t>157512</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>200884</t>
+          <t>204144</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,96%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>267889</t>
+          <t>267628</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>297840</t>
+          <t>297554</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>74,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>249912</t>
+          <t>249696</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>284198</t>
+          <t>283579</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>67,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>529243</t>
+          <t>525983</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>572826</t>
+          <t>572615</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>78,43%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25086</t>
+          <t>24819</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45868</t>
+          <t>46757</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,82 +2120,82 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>23,0%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>42041</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>31143</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>54306</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>20,24%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>15,0%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>26,15%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>76813</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>61283</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>92711</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>18,69%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>14,91%</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
           <t>22,56%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>42041</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>30714</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>54265</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>20,24%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>14,79%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>26,13%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>76813</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>61976</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>92937</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>18,69%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>15,08%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>22,61%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>157440</t>
+          <t>156551</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>178222</t>
+          <t>178489</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,82 +2233,82 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>77,0%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>87,79%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>165627</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>153362</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>176525</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>79,76%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>73,85%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>85,0%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>334163</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>318265</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>349693</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>81,31%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t>77,44%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>87,66%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>165627</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>153403</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>176954</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>79,76%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>73,87%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>85,21%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>334163</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>318039</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>349000</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>81,31%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>77,39%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>85,09%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>45977</t>
+          <t>45580</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>72811</t>
+          <t>73017</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>72847</t>
+          <t>72047</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>103121</t>
+          <t>103605</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>124496</t>
+          <t>126865</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>167675</t>
+          <t>164989</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,11%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>198000</t>
+          <t>197794</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>224834</t>
+          <t>225231</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>174082</t>
+          <t>173598</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>204356</t>
+          <t>205156</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>62,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>380339</t>
+          <t>383025</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>423518</t>
+          <t>421149</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>76,85%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>91223</t>
+          <t>92471</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>129851</t>
+          <t>131259</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>147478</t>
+          <t>147399</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>192328</t>
+          <t>191101</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>250815</t>
+          <t>253115</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>309384</t>
+          <t>309325</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>484291</t>
+          <t>482883</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>522919</t>
+          <t>521671</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>445891</t>
+          <t>447118</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>490741</t>
+          <t>490820</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>70,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>942977</t>
+          <t>943036</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1001546</t>
+          <t>999246</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>79,79%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>81025</t>
+          <t>78694</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>119565</t>
+          <t>118565</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>128670</t>
+          <t>128270</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>175800</t>
+          <t>175700</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,47 +3184,47 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
+          <t>16,37%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>22,42%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>250850</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>224289</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>281586</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
           <t>16,42%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>22,44%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>250850</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>226334</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>283042</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>16,42%</t>
-        </is>
-      </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,44%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>624230</t>
+          <t>625230</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>662770</t>
+          <t>665101</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>607711</t>
+          <t>607811</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>654841</t>
+          <t>655241</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,47 +3297,47 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
+          <t>83,63%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>1241</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>1276456</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>1245720</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>1303017</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
           <t>83,58%</t>
         </is>
       </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>1241</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>1276456</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>1244264</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>1300972</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>83,58%</t>
-        </is>
-      </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,31%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>521268</t>
+          <t>515224</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>607385</t>
+          <t>602739</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>774989</t>
+          <t>774864</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>873724</t>
+          <t>872861</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1317955</t>
+          <t>1319432</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1449133</t>
+          <t>1450792</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,8%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2668274</t>
+          <t>2672920</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2754391</t>
+          <t>2760435</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2504533</t>
+          <t>2505396</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2603268</t>
+          <t>2603393</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5204782</t>
+          <t>5203123</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5335960</t>
+          <t>5334483</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>80,17%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado un servicio de urgencias en el último año en 2012</t>
+          <t>Población que ha utilizado un servicio de urgencias en el último año en 2012 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>85587</t>
+          <t>85434</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>118959</t>
+          <t>117241</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>95045</t>
+          <t>94836</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>131373</t>
+          <t>127492</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>188586</t>
+          <t>189730</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>236478</t>
+          <t>237171</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>40,89%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>175052</t>
+          <t>176770</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>208424</t>
+          <t>208577</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>70,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>154694</t>
+          <t>158575</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>191022</t>
+          <t>191231</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>66,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>343600</t>
+          <t>342907</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>391492</t>
+          <t>390348</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>59,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>67,29%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>111554</t>
+          <t>112870</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>151110</t>
+          <t>152229</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>176635</t>
+          <t>178194</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>224646</t>
+          <t>224409</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>300417</t>
+          <t>299833</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>360434</t>
+          <t>361787</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>35,15%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>354417</t>
+          <t>353298</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>393973</t>
+          <t>392657</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>299119</t>
+          <t>299356</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>347130</t>
+          <t>345571</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>65,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>668858</t>
+          <t>667505</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>728875</t>
+          <t>729459</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>70,87%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>62018</t>
+          <t>62055</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>91414</t>
+          <t>90965</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>79261</t>
+          <t>79114</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>113665</t>
+          <t>115337</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>148952</t>
+          <t>150383</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>196020</t>
+          <t>194944</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,31%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>232632</t>
+          <t>233081</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>262028</t>
+          <t>261991</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>227355</t>
+          <t>225683</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>261759</t>
+          <t>261906</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>469046</t>
+          <t>470122</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>516114</t>
+          <t>514683</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>70,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,39%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64137</t>
+          <t>66287</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>98584</t>
+          <t>98758</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>88194</t>
+          <t>87867</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>124892</t>
+          <t>124613</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>160736</t>
+          <t>159034</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>208545</t>
+          <t>210083</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,57%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>275398</t>
+          <t>275224</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>309845</t>
+          <t>307695</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>263100</t>
+          <t>263379</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>299798</t>
+          <t>300125</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>553429</t>
+          <t>551891</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>601238</t>
+          <t>602940</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,63%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>79,13%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26678</t>
+          <t>27174</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48509</t>
+          <t>48983</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>65942</t>
+          <t>64058</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>94987</t>
+          <t>93409</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>97447</t>
+          <t>98362</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>135348</t>
+          <t>135608</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,38%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>164109</t>
+          <t>163635</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>185940</t>
+          <t>185444</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>124604</t>
+          <t>126182</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>153649</t>
+          <t>155533</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>57,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>70,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>296861</t>
+          <t>296601</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>334762</t>
+          <t>333847</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>68,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>77,24%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>51437</t>
+          <t>50126</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>79160</t>
+          <t>78077</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>79805</t>
+          <t>81449</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>111185</t>
+          <t>112346</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>141078</t>
+          <t>139951</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>182789</t>
+          <t>184316</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>33,27%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>194821</t>
+          <t>195904</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>222544</t>
+          <t>223855</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>71,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>168846</t>
+          <t>167685</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>200226</t>
+          <t>198582</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>59,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>371223</t>
+          <t>369696</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>412934</t>
+          <t>414061</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>74,74%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>126305</t>
+          <t>123442</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>169513</t>
+          <t>168405</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>163251</t>
+          <t>165772</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>213863</t>
+          <t>213664</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>303465</t>
+          <t>301902</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>369391</t>
+          <t>363583</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>26,8%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>493275</t>
+          <t>494383</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>536483</t>
+          <t>539346</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>479990</t>
+          <t>480189</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>530602</t>
+          <t>528081</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>69,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>987250</t>
+          <t>993058</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1053176</t>
+          <t>1054739</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>77,75%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>53572</t>
+          <t>53169</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>89123</t>
+          <t>88231</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>86683</t>
+          <t>85963</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>128222</t>
+          <t>126101</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>151726</t>
+          <t>151661</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>203789</t>
+          <t>204335</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,77%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>688021</t>
+          <t>688913</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>723572</t>
+          <t>723975</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>694662</t>
+          <t>696783</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>736201</t>
+          <t>736921</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1396239</t>
+          <t>1395693</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1448302</t>
+          <t>1448367</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>658662</t>
+          <t>660984</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>759263</t>
+          <t>758293</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>927222</t>
+          <t>928969</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1038189</t>
+          <t>1042891</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1615706</t>
+          <t>1614116</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1763105</t>
+          <t>1764599</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,28%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2664835</t>
+          <t>2665805</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2765436</t>
+          <t>2763114</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2517014</t>
+          <t>2512312</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2627981</t>
+          <t>2626234</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>70,67%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5216196</t>
+          <t>5214702</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5363595</t>
+          <t>5365185</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>76,87%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado un servicio de urgencias en el último año en 2016</t>
+          <t>Población que ha utilizado un servicio de urgencias en el último año en 2016 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>68060</t>
+          <t>67901</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>101700</t>
+          <t>98858</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>90497</t>
+          <t>89348</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>121401</t>
+          <t>122416</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>164666</t>
+          <t>164902</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>211590</t>
+          <t>210528</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>36,26%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>192061</t>
+          <t>194903</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>225701</t>
+          <t>225860</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>165483</t>
+          <t>164468</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>196387</t>
+          <t>197536</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,68%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>68,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>369055</t>
+          <t>370117</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>415979</t>
+          <t>415743</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>71,6%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67929</t>
+          <t>66654</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>101404</t>
+          <t>100186</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>92219</t>
+          <t>91158</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>131811</t>
+          <t>130162</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>166038</t>
+          <t>170092</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>217394</t>
+          <t>222526</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,7%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>401171</t>
+          <t>402389</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>434646</t>
+          <t>435921</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>391273</t>
+          <t>392922</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>430865</t>
+          <t>431926</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>808265</t>
+          <t>803133</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>859621</t>
+          <t>855567</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>83,42%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27432</t>
+          <t>27178</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49015</t>
+          <t>48970</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35712</t>
+          <t>35485</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61193</t>
+          <t>62221</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>69388</t>
+          <t>68297</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>102782</t>
+          <t>103554</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>16,01%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>264099</t>
+          <t>264144</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>285682</t>
+          <t>285936</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>272615</t>
+          <t>271587</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>298096</t>
+          <t>298323</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>544140</t>
+          <t>543368</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>577534</t>
+          <t>578625</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,44%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>81417</t>
+          <t>79629</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>115068</t>
+          <t>114692</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>106045</t>
+          <t>105087</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>144527</t>
+          <t>145436</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>195391</t>
+          <t>196852</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>249127</t>
+          <t>253490</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,61%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>251938</t>
+          <t>252314</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>285589</t>
+          <t>287377</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>242756</t>
+          <t>241847</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>281238</t>
+          <t>282196</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>505162</t>
+          <t>500799</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>558898</t>
+          <t>557437</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>66,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>73,9%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18467</t>
+          <t>17153</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38173</t>
+          <t>35926</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20893</t>
+          <t>21710</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40455</t>
+          <t>42362</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>44462</t>
+          <t>43847</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>71509</t>
+          <t>72134</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,91%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>170791</t>
+          <t>173038</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>190497</t>
+          <t>191811</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>177264</t>
+          <t>175357</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>196826</t>
+          <t>196009</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>355175</t>
+          <t>354550</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>382222</t>
+          <t>382837</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,72%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>45937</t>
+          <t>44098</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>72668</t>
+          <t>71761</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>62468</t>
+          <t>62222</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>91868</t>
+          <t>91612</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>113944</t>
+          <t>114371</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>154386</t>
+          <t>154836</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,87%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>190455</t>
+          <t>191362</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>217186</t>
+          <t>219025</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>72,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>83,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>181247</t>
+          <t>181503</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>210647</t>
+          <t>210893</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>77,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>381852</t>
+          <t>381402</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>422294</t>
+          <t>421867</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>78,67%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>58801</t>
+          <t>58950</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>93004</t>
+          <t>95901</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>104889</t>
+          <t>103892</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>147153</t>
+          <t>146872</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>174055</t>
+          <t>174551</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>227787</t>
+          <t>227796</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>563554</t>
+          <t>560657</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>597757</t>
+          <t>597608</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>542870</t>
+          <t>543151</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>585134</t>
+          <t>586131</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1118794</t>
+          <t>1118785</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1172526</t>
+          <t>1172030</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9640,7 +9640,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>87,04%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>86945</t>
+          <t>84960</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>125223</t>
+          <t>123530</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>122208</t>
+          <t>121505</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>165656</t>
+          <t>165970</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>216413</t>
+          <t>218561</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>275413</t>
+          <t>277371</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,28%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>653360</t>
+          <t>655053</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>691638</t>
+          <t>693623</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>660511</t>
+          <t>660197</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>703959</t>
+          <t>704662</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1329337</t>
+          <t>1327379</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1388337</t>
+          <t>1386189</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,38%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>518647</t>
+          <t>521233</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>608351</t>
+          <t>605503</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>710011</t>
+          <t>714275</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>809947</t>
+          <t>817333</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1257784</t>
+          <t>1256781</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1393367</t>
+          <t>1391939</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,11%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2775333</t>
+          <t>2778181</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2865037</t>
+          <t>2862451</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2728136</t>
+          <t>2720750</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2828072</t>
+          <t>2823808</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5528400</t>
+          <t>5529828</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5663983</t>
+          <t>5664986</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>81,84%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado un servicio de urgencias en el último año en 2023</t>
+          <t>Población que ha utilizado un servicio de urgencias en el último año en 2023 (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>87706</t>
+          <t>87017</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>128697</t>
+          <t>129162</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>99314</t>
+          <t>100597</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>127984</t>
+          <t>127867</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>194356</t>
+          <t>195332</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>245698</t>
+          <t>245614</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>40,86%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>182746</t>
+          <t>182281</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>223737</t>
+          <t>224426</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>58,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>72,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>161651</t>
+          <t>161768</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>190321</t>
+          <t>189038</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>65,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>355379</t>
+          <t>355463</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>406721</t>
+          <t>405745</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>59,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>67,5%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>61267</t>
+          <t>60755</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>105220</t>
+          <t>102342</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>88594</t>
+          <t>89148</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>120496</t>
+          <t>120020</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>155793</t>
+          <t>154206</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>209107</t>
+          <t>208240</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,17%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>413170</t>
+          <t>416048</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>457123</t>
+          <t>457635</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>80,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>393597</t>
+          <t>394073</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>425499</t>
+          <t>424945</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>76,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>823376</t>
+          <t>824243</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>876690</t>
+          <t>878277</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>85,06%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>58202</t>
+          <t>58316</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>87309</t>
+          <t>88042</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>98368</t>
+          <t>97860</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>128865</t>
+          <t>128178</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>164804</t>
+          <t>161778</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>205033</t>
+          <t>204469</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,76%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>228741</t>
+          <t>228008</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>257848</t>
+          <t>257734</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>219717</t>
+          <t>220404</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>250214</t>
+          <t>250722</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>63,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>459599</t>
+          <t>460163</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>499828</t>
+          <t>502854</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>69,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,66%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>59091</t>
+          <t>58797</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>96570</t>
+          <t>95552</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55717</t>
+          <t>55642</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>119741</t>
+          <t>120193</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>122141</t>
+          <t>119382</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>205150</t>
+          <t>201748</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>25,65%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>214233</t>
+          <t>215251</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>251712</t>
+          <t>252006</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>69,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>355977</t>
+          <t>355525</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>420001</t>
+          <t>420076</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>74,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>581371</t>
+          <t>584773</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>664380</t>
+          <t>667139</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,82%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10883</t>
+          <t>11029</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25361</t>
+          <t>27543</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>6619</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14779</t>
+          <t>14876</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20028</t>
+          <t>20020</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36573</t>
+          <t>36726</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>153381</t>
+          <t>151199</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>167859</t>
+          <t>167713</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>193877</t>
+          <t>193780</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>201971</t>
+          <t>202037</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>350825</t>
+          <t>350672</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>367370</t>
+          <t>367378</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,7 +12272,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>56252</t>
+          <t>57030</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>81932</t>
+          <t>81896</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>63926</t>
+          <t>64236</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>87667</t>
+          <t>87937</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>127261</t>
+          <t>127347</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>163022</t>
+          <t>161106</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>30,59%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>187704</t>
+          <t>187740</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>213384</t>
+          <t>212606</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>69,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>169389</t>
+          <t>169119</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>193130</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>363670</t>
+          <t>365586</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>399431</t>
+          <t>399345</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>75,82%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>140486</t>
+          <t>143965</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>196396</t>
+          <t>196429</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,7 +12775,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>287110</t>
+          <t>285380</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>674783</t>
+          <t>640378</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>440866</t>
+          <t>442388</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>926737</t>
+          <t>969565</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>65,99%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>427883</t>
+          <t>427850</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>483793</t>
+          <t>480314</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12893,7 +12893,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>76,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>170307</t>
+          <t>204712</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>557980</t>
+          <t>559710</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>66,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>542632</t>
+          <t>499804</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1028503</t>
+          <t>1026981</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>69,89%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>34516</t>
+          <t>37924</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>129638</t>
+          <t>131409</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>95392</t>
+          <t>95312</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>128999</t>
+          <t>128343</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>121667</t>
+          <t>125273</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>247353</t>
+          <t>246991</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,03%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>799082</t>
+          <t>797311</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>894204</t>
+          <t>890796</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>585862</t>
+          <t>586518</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>619469</t>
+          <t>619549</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1396229</t>
+          <t>1396591</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1521915</t>
+          <t>1518309</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,38%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>527034</t>
+          <t>524524</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>749197</t>
+          <t>755954</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>871974</t>
+          <t>873901</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1578998</t>
+          <t>1535499</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1504178</t>
+          <t>1526592</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2288957</t>
+          <t>2323565</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,67%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2708867</t>
+          <t>2702110</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2931030</t>
+          <t>2933540</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2074693</t>
+          <t>2118192</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2781717</t>
+          <t>2779790</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4822798</t>
+          <t>4788190</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5607577</t>
+          <t>5585163</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>67,33%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>78,53%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P21_R-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29015</t>
+          <t>29074</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52134</t>
+          <t>51003</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44437</t>
+          <t>42918</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>71159</t>
+          <t>70018</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>77731</t>
+          <t>76094</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>112387</t>
+          <t>113883</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,33%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>220876</t>
+          <t>222007</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>243995</t>
+          <t>243936</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>81,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>189679</t>
+          <t>190820</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>216401</t>
+          <t>217920</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>421461</t>
+          <t>419965</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>456117</t>
+          <t>457754</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,75%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>61937</t>
+          <t>59880</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>94979</t>
+          <t>94596</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>110331</t>
+          <t>110157</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>147318</t>
+          <t>147939</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>178556</t>
+          <t>179588</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>228189</t>
+          <t>229893</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,06%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>398096</t>
+          <t>398479</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>431138</t>
+          <t>433195</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>356631</t>
+          <t>356010</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>393618</t>
+          <t>393792</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>70,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>768835</t>
+          <t>767131</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>818468</t>
+          <t>817436</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>76,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>81,99%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>54943</t>
+          <t>54531</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>84804</t>
+          <t>84720</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>70582</t>
+          <t>71388</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>102957</t>
+          <t>103745</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>132411</t>
+          <t>133275</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>176963</t>
+          <t>177650</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>27,15%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>234042</t>
+          <t>234126</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>263903</t>
+          <t>264315</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>232455</t>
+          <t>231667</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>264830</t>
+          <t>264024</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>78,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>477295</t>
+          <t>476608</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>521847</t>
+          <t>520983</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>72,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,63%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>61117</t>
+          <t>59837</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>91043</t>
+          <t>90674</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>87877</t>
+          <t>88027</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>121760</t>
+          <t>119612</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>157512</t>
+          <t>156760</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>204144</t>
+          <t>200080</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,4%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>267628</t>
+          <t>267997</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>297554</t>
+          <t>298834</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>249696</t>
+          <t>251844</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>283579</t>
+          <t>283429</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>67,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>525983</t>
+          <t>530047</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>572615</t>
+          <t>573367</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>78,53%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24819</t>
+          <t>24331</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>46757</t>
+          <t>45999</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31143</t>
+          <t>30477</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>54306</t>
+          <t>55954</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>61283</t>
+          <t>61715</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>92711</t>
+          <t>93198</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,68%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>156551</t>
+          <t>157309</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>178489</t>
+          <t>178977</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>77,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>153362</t>
+          <t>151714</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>176525</t>
+          <t>177191</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>73,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>318265</t>
+          <t>317778</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>349693</t>
+          <t>349261</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>84,98%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>45580</t>
+          <t>45590</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>73017</t>
+          <t>74457</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>72047</t>
+          <t>72146</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>103605</t>
+          <t>102838</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>126865</t>
+          <t>124890</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>164989</t>
+          <t>167038</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,48%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>197794</t>
+          <t>196354</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>225231</t>
+          <t>225221</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>72,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>173598</t>
+          <t>174365</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>205156</t>
+          <t>205057</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>383025</t>
+          <t>380976</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>421149</t>
+          <t>423124</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>77,21%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>92471</t>
+          <t>91510</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>131259</t>
+          <t>132548</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>147399</t>
+          <t>146201</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>191101</t>
+          <t>190097</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>253115</t>
+          <t>250450</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>309325</t>
+          <t>309136</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,68%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>482883</t>
+          <t>481594</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>521671</t>
+          <t>522632</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>447118</t>
+          <t>448122</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>490820</t>
+          <t>492018</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>70,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>943036</t>
+          <t>943225</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>999246</t>
+          <t>1001911</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>80,0%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>78694</t>
+          <t>80892</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>118565</t>
+          <t>119903</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>128270</t>
+          <t>129044</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>175700</t>
+          <t>175100</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>224289</t>
+          <t>221895</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>281586</t>
+          <t>277911</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,2%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>625230</t>
+          <t>623892</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>665101</t>
+          <t>662903</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>607811</t>
+          <t>608411</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>655241</t>
+          <t>654467</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1245720</t>
+          <t>1249395</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1303017</t>
+          <t>1305411</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>85,47%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>515224</t>
+          <t>520496</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>602739</t>
+          <t>605763</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>774864</t>
+          <t>772794</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>872861</t>
+          <t>869588</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1319432</t>
+          <t>1316431</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1450792</t>
+          <t>1454107</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,85%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2672920</t>
+          <t>2669896</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2760435</t>
+          <t>2755163</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2505396</t>
+          <t>2508669</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2603393</t>
+          <t>2605463</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>77,12%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5203123</t>
+          <t>5199808</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5334483</t>
+          <t>5337484</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>80,22%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>85434</t>
+          <t>83412</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>117241</t>
+          <t>116531</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>94836</t>
+          <t>94411</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>127492</t>
+          <t>129952</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>45,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>189730</t>
+          <t>189521</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>237171</t>
+          <t>237375</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>40,92%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>176770</t>
+          <t>177480</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>208577</t>
+          <t>210599</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>158575</t>
+          <t>156115</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>191231</t>
+          <t>191656</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>54,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>67,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>342907</t>
+          <t>342703</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>390348</t>
+          <t>390557</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,11%</t>
+          <t>59,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>67,33%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>112870</t>
+          <t>112107</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>152229</t>
+          <t>153553</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>178194</t>
+          <t>178855</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>224409</t>
+          <t>223082</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>42,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>299833</t>
+          <t>299374</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>361787</t>
+          <t>359768</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>34,95%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>353298</t>
+          <t>351974</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>392657</t>
+          <t>393420</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>69,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>77,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>299356</t>
+          <t>300683</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>345571</t>
+          <t>344910</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>65,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>667505</t>
+          <t>669524</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>729459</t>
+          <t>729918</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>65,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>70,91%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>62055</t>
+          <t>61232</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>90965</t>
+          <t>91547</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>79114</t>
+          <t>80218</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>115337</t>
+          <t>114947</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>150383</t>
+          <t>150251</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>194944</t>
+          <t>196715</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,58%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>233081</t>
+          <t>232499</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>261991</t>
+          <t>262814</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>225683</t>
+          <t>226073</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>261906</t>
+          <t>260802</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>66,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>470122</t>
+          <t>468351</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>514683</t>
+          <t>514815</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>77,41%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>66287</t>
+          <t>65795</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>98758</t>
+          <t>98548</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>87867</t>
+          <t>87675</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>124613</t>
+          <t>123228</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>159034</t>
+          <t>159815</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>210083</t>
+          <t>210031</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,56%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>275224</t>
+          <t>275434</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>307695</t>
+          <t>308187</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>263379</t>
+          <t>264764</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>300125</t>
+          <t>300317</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>551891</t>
+          <t>551943</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>602940</t>
+          <t>602159</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>79,03%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27174</t>
+          <t>26167</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48983</t>
+          <t>48371</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>64058</t>
+          <t>65022</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>93409</t>
+          <t>93684</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>98362</t>
+          <t>98821</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>135608</t>
+          <t>134333</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,08%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>163635</t>
+          <t>164247</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>185444</t>
+          <t>186451</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>126182</t>
+          <t>125907</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>155533</t>
+          <t>154569</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>57,46%</t>
+          <t>57,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,83%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>296601</t>
+          <t>297876</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>333847</t>
+          <t>333388</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>68,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>77,14%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>50126</t>
+          <t>52201</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>78077</t>
+          <t>80196</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>81449</t>
+          <t>80881</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>112346</t>
+          <t>112897</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>40,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>139951</t>
+          <t>139421</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>184316</t>
+          <t>181763</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>32,81%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>195904</t>
+          <t>193785</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>223855</t>
+          <t>221780</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>70,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>167685</t>
+          <t>167134</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>198582</t>
+          <t>199150</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>59,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>369696</t>
+          <t>372249</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>414061</t>
+          <t>414591</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>67,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>74,83%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>123442</t>
+          <t>125271</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>168405</t>
+          <t>171857</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>165772</t>
+          <t>162862</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>213664</t>
+          <t>213158</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>301902</t>
+          <t>301074</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>363583</t>
+          <t>370075</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>27,28%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>494383</t>
+          <t>490931</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>539346</t>
+          <t>537517</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>480189</t>
+          <t>480695</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>528081</t>
+          <t>530991</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>993058</t>
+          <t>986566</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1054739</t>
+          <t>1055567</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>77,81%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>53169</t>
+          <t>53329</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>88231</t>
+          <t>88196</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>85963</t>
+          <t>87155</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>126101</t>
+          <t>128125</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>151661</t>
+          <t>150198</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>204335</t>
+          <t>204640</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,79%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>688913</t>
+          <t>688948</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>723975</t>
+          <t>723815</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>696783</t>
+          <t>694759</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>736921</t>
+          <t>735729</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1395693</t>
+          <t>1395388</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1448367</t>
+          <t>1449830</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,61%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>660984</t>
+          <t>653775</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>758293</t>
+          <t>753657</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>928969</t>
+          <t>931378</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1042891</t>
+          <t>1040224</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1614116</t>
+          <t>1617893</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1764599</t>
+          <t>1765029</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,29%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2665805</t>
+          <t>2670441</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2763114</t>
+          <t>2770323</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>77,99%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2512312</t>
+          <t>2514979</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2626234</t>
+          <t>2623825</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5214702</t>
+          <t>5214272</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5365185</t>
+          <t>5361408</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>76,82%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>67901</t>
+          <t>68850</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>98858</t>
+          <t>101621</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>89348</t>
+          <t>87979</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>122416</t>
+          <t>121951</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>164902</t>
+          <t>165239</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>210528</t>
+          <t>210686</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,28%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>194903</t>
+          <t>192140</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>225860</t>
+          <t>224911</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>76,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>164468</t>
+          <t>164933</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>197536</t>
+          <t>198905</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,33%</t>
+          <t>57,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>69,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>370117</t>
+          <t>369959</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>415743</t>
+          <t>415406</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>71,54%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>66654</t>
+          <t>66608</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>100186</t>
+          <t>101225</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>91158</t>
+          <t>90327</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>130162</t>
+          <t>129212</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>170092</t>
+          <t>169440</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>222526</t>
+          <t>219068</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,36%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>402389</t>
+          <t>401350</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>435921</t>
+          <t>435967</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>392922</t>
+          <t>393872</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>431926</t>
+          <t>432757</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>803133</t>
+          <t>806591</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>855567</t>
+          <t>856219</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,48%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27178</t>
+          <t>27818</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48970</t>
+          <t>49624</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35485</t>
+          <t>36010</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62221</t>
+          <t>61555</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>68297</t>
+          <t>67202</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>103554</t>
+          <t>101741</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,73%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>264144</t>
+          <t>263490</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>285936</t>
+          <t>285296</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>271587</t>
+          <t>272253</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>298323</t>
+          <t>297798</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>543368</t>
+          <t>545181</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>578625</t>
+          <t>579720</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,61%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>79629</t>
+          <t>79840</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>114692</t>
+          <t>116914</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>105087</t>
+          <t>106215</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>145436</t>
+          <t>145700</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>196852</t>
+          <t>196396</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>253490</t>
+          <t>249655</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,1%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>252314</t>
+          <t>250092</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>287377</t>
+          <t>287166</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>68,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>241847</t>
+          <t>241583</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>282196</t>
+          <t>281068</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,45%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>500799</t>
+          <t>504634</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>557437</t>
+          <t>557893</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,39%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>73,96%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17153</t>
+          <t>17164</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35926</t>
+          <t>36040</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21710</t>
+          <t>21652</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42362</t>
+          <t>40578</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>43847</t>
+          <t>42948</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>72134</t>
+          <t>71326</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,72%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>173038</t>
+          <t>172924</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>191811</t>
+          <t>191800</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>175357</t>
+          <t>177141</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>196009</t>
+          <t>196067</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>354550</t>
+          <t>355358</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>382837</t>
+          <t>383736</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,93%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44098</t>
+          <t>45721</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>71761</t>
+          <t>71910</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>62222</t>
+          <t>60730</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>91612</t>
+          <t>91646</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>114371</t>
+          <t>116756</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>154836</t>
+          <t>158216</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>29,5%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>191362</t>
+          <t>191213</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>219025</t>
+          <t>217402</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>72,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>181503</t>
+          <t>181469</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>210893</t>
+          <t>212385</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>66,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>381402</t>
+          <t>378022</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>421867</t>
+          <t>419482</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>78,23%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>58950</t>
+          <t>58745</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>95901</t>
+          <t>93567</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>103892</t>
+          <t>106838</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>146872</t>
+          <t>148121</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>174551</t>
+          <t>174321</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>227796</t>
+          <t>226190</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,8%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>560657</t>
+          <t>562991</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>597608</t>
+          <t>597813</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>543151</t>
+          <t>541902</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>586131</t>
+          <t>583185</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1118785</t>
+          <t>1120391</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1172030</t>
+          <t>1172260</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>87,05%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>84960</t>
+          <t>84906</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>123530</t>
+          <t>124406</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>121505</t>
+          <t>121655</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>165970</t>
+          <t>165019</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>218561</t>
+          <t>216893</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>277371</t>
+          <t>274556</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,11%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>655053</t>
+          <t>654177</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>693623</t>
+          <t>693677</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>660197</t>
+          <t>661148</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>704662</t>
+          <t>704512</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1327379</t>
+          <t>1330194</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1386189</t>
+          <t>1387857</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,48%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>521233</t>
+          <t>525366</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>605503</t>
+          <t>610908</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>714275</t>
+          <t>713789</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>817333</t>
+          <t>813841</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1256781</t>
+          <t>1264567</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1391939</t>
+          <t>1399609</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,22%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2778181</t>
+          <t>2772776</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2862451</t>
+          <t>2858318</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2720750</t>
+          <t>2724242</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2823808</t>
+          <t>2824294</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>77,0%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5529828</t>
+          <t>5522158</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5664986</t>
+          <t>5657200</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>81,73%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>106964</t>
+          <t>106088</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>87017</t>
+          <t>89049</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>129162</t>
+          <t>123769</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>113473</t>
+          <t>121762</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>100597</t>
+          <t>108283</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>127867</t>
+          <t>137246</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>220436</t>
+          <t>227850</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>195332</t>
+          <t>205124</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>245614</t>
+          <t>250109</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>39,39%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>204479</t>
+          <t>212757</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>182281</t>
+          <t>195076</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>224426</t>
+          <t>229796</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>61,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,06%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>176162</t>
+          <t>194299</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>161768</t>
+          <t>178815</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>189038</t>
+          <t>207778</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,27%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>380641</t>
+          <t>407056</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>355463</t>
+          <t>384797</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>405745</t>
+          <t>429782</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>67,69%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>78622</t>
+          <t>80932</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>60755</t>
+          <t>61888</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>102342</t>
+          <t>102527</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>103078</t>
+          <t>108245</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>89148</t>
+          <t>91936</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>120020</t>
+          <t>125064</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>181700</t>
+          <t>189177</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>154206</t>
+          <t>161973</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>208240</t>
+          <t>215235</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,0%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>439768</t>
+          <t>449715</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>416048</t>
+          <t>428120</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>457635</t>
+          <t>468759</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>411015</t>
+          <t>437377</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>394073</t>
+          <t>420558</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>424945</t>
+          <t>453686</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>83,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>850783</t>
+          <t>887092</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>824243</t>
+          <t>861034</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>878277</t>
+          <t>914296</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>84,95%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514093</t>
+          <t>545622</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514093</t>
+          <t>545622</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514093</t>
+          <t>545622</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1032483</t>
+          <t>1076269</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1032483</t>
+          <t>1076269</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1032483</t>
+          <t>1076269</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>71809</t>
+          <t>74776</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>58316</t>
+          <t>61692</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>88042</t>
+          <t>91471</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>112167</t>
+          <t>114616</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>97860</t>
+          <t>99973</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>128178</t>
+          <t>129788</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>183976</t>
+          <t>189392</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>161778</t>
+          <t>170534</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>204469</t>
+          <t>213002</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>31,7%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>244241</t>
+          <t>241217</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>228008</t>
+          <t>224522</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>257734</t>
+          <t>254301</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>76,34%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>236415</t>
+          <t>241221</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>220404</t>
+          <t>226049</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>250722</t>
+          <t>255864</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>67,79%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>63,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>480656</t>
+          <t>482438</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>460163</t>
+          <t>458828</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>502854</t>
+          <t>501296</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>72,32%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>68,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>74,62%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>348582</t>
+          <t>355837</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>348582</t>
+          <t>355837</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>348582</t>
+          <t>355837</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>664632</t>
+          <t>671830</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>664632</t>
+          <t>671830</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>664632</t>
+          <t>671830</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>76327</t>
+          <t>90105</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>58797</t>
+          <t>71900</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>95552</t>
+          <t>117738</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>92154</t>
+          <t>106735</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55642</t>
+          <t>89188</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>120193</t>
+          <t>126279</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>168481</t>
+          <t>196840</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>119382</t>
+          <t>169830</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>201748</t>
+          <t>228584</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>28,82%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>234476</t>
+          <t>281070</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>215251</t>
+          <t>253437</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>252006</t>
+          <t>299275</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>383564</t>
+          <t>315226</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>355525</t>
+          <t>295682</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>420076</t>
+          <t>332773</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>70,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>618040</t>
+          <t>596296</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>584773</t>
+          <t>564552</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>667139</t>
+          <t>623306</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>71,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>78,59%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>310803</t>
+          <t>371175</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>310803</t>
+          <t>371175</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>310803</t>
+          <t>371175</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>786521</t>
+          <t>793136</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>786521</t>
+          <t>793136</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>786521</t>
+          <t>793136</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>17208</t>
+          <t>18799</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11029</t>
+          <t>11167</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27543</t>
+          <t>28419</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,17 +12104,17 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>10092</t>
+          <t>11004</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6619</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14876</t>
+          <t>15531</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>27300</t>
+          <t>29803</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20020</t>
+          <t>22268</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36726</t>
+          <t>39404</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>161534</t>
+          <t>186866</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>151199</t>
+          <t>177246</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>167713</t>
+          <t>194498</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,17 +12217,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>198564</t>
+          <t>216211</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>193780</t>
+          <t>211684</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>202037</t>
+          <t>220094</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>360098</t>
+          <t>403076</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>350672</t>
+          <t>393475</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>367378</t>
+          <t>410611</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,86%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>68786</t>
+          <t>68278</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>57030</t>
+          <t>56856</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>81896</t>
+          <t>81908</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>75774</t>
+          <t>77225</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>64236</t>
+          <t>65111</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>87937</t>
+          <t>89543</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>144560</t>
+          <t>145504</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>127347</t>
+          <t>128521</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>161106</t>
+          <t>163662</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,62%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>200850</t>
+          <t>202429</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>187740</t>
+          <t>188799</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>212606</t>
+          <t>213851</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>79,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>181282</t>
+          <t>186525</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>169119</t>
+          <t>174207</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>198639</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>382132</t>
+          <t>388953</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>365586</t>
+          <t>370795</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>399345</t>
+          <t>405936</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>72,78%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>69,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>75,95%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>167436</t>
+          <t>192031</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>143965</t>
+          <t>165159</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>196429</t>
+          <t>220058</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>428512</t>
+          <t>266194</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>285380</t>
+          <t>241859</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>640378</t>
+          <t>291176</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>595948</t>
+          <t>458224</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>442388</t>
+          <t>421060</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>969565</t>
+          <t>495403</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>33,31%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>456843</t>
+          <t>527656</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>427850</t>
+          <t>499629</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>480314</t>
+          <t>554528</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>73,32%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>416578</t>
+          <t>501510</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>204712</t>
+          <t>476528</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>559710</t>
+          <t>525845</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>65,33%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>62,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>873421</t>
+          <t>1029167</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>499804</t>
+          <t>991988</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1026981</t>
+          <t>1066331</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>69,19%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>66,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>71,69%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>845090</t>
+          <t>767704</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>845090</t>
+          <t>767704</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>845090</t>
+          <t>767704</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1469369</t>
+          <t>1487391</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1469369</t>
+          <t>1487391</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1469369</t>
+          <t>1487391</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>89772</t>
+          <t>102172</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>37924</t>
+          <t>85595</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>131409</t>
+          <t>123987</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>111238</t>
+          <t>128949</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>95312</t>
+          <t>110157</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>128343</t>
+          <t>148123</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>201010</t>
+          <t>231122</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>125273</t>
+          <t>204716</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>246991</t>
+          <t>260139</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,98%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>838948</t>
+          <t>695900</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>797311</t>
+          <t>674085</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>890796</t>
+          <t>712477</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>603623</t>
+          <t>701067</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>586518</t>
+          <t>681893</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>619549</t>
+          <t>719859</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>82,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1442572</t>
+          <t>1396966</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1396591</t>
+          <t>1367949</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1518309</t>
+          <t>1423372</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>87,43%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>714861</t>
+          <t>830016</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>714861</t>
+          <t>830016</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>714861</t>
+          <t>830016</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1643582</t>
+          <t>1628088</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1643582</t>
+          <t>1628088</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1643582</t>
+          <t>1628088</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>676924</t>
+          <t>733182</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>524524</t>
+          <t>680550</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>755954</t>
+          <t>786603</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1046486</t>
+          <t>934729</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>873901</t>
+          <t>888878</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1535499</t>
+          <t>978948</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1723411</t>
+          <t>1667911</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1526592</t>
+          <t>1598604</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2323565</t>
+          <t>1743154</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>24,01%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2781140</t>
+          <t>2797610</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2702110</t>
+          <t>2744189</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2933540</t>
+          <t>2850242</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2607205</t>
+          <t>2793437</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2118192</t>
+          <t>2749218</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2779790</t>
+          <t>2839288</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>5388344</t>
+          <t>5591047</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4788190</t>
+          <t>5515804</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5585163</t>
+          <t>5660354</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>77,98%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3458064</t>
+          <t>3530792</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3458064</t>
+          <t>3530792</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3458064</t>
+          <t>3530792</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3653691</t>
+          <t>3728166</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3653691</t>
+          <t>3728166</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3653691</t>
+          <t>3728166</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7111755</t>
+          <t>7258958</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7111755</t>
+          <t>7258958</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7111755</t>
+          <t>7258958</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
